--- a/bases_historicas/base_consolidada_07-2026.xlsx
+++ b/bases_historicas/base_consolidada_07-2026.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY157"/>
+  <dimension ref="A1:AY188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -27095,165 +27095,5448 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026 - 05</t>
-        </is>
-      </c>
-      <c r="B157" t="n">
-        <v>0</v>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Algodão</t>
+        </is>
       </c>
       <c r="C157" t="n">
-        <v>0</v>
+        <v>10.39565598238795</v>
       </c>
       <c r="D157" t="n">
-        <v>0</v>
+        <v>8.631302797166597</v>
       </c>
       <c r="E157" t="n">
-        <v>0</v>
+        <v>9.714813001393827</v>
       </c>
       <c r="F157" t="n">
-        <v>0</v>
+        <v>8.47660848315032</v>
       </c>
       <c r="G157" t="n">
-        <v>0</v>
+        <v>5.135040518924654</v>
       </c>
       <c r="H157" t="n">
-        <v>0</v>
+        <v>6.621678077322716</v>
       </c>
       <c r="I157" t="n">
-        <v>0</v>
+        <v>6.220092799045068</v>
       </c>
       <c r="J157" t="n">
-        <v>0</v>
+        <v>4.282227288258426</v>
       </c>
       <c r="K157" t="n">
-        <v>0</v>
+        <v>3.995782294830768</v>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
+        <v>4.846943698233574</v>
       </c>
       <c r="M157" t="n">
-        <v>0</v>
+        <v>6.268523027327628</v>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>8.290011847559931</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>9.453282567719558</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>7.861780211460168</v>
       </c>
       <c r="Q157" t="n">
-        <v>0</v>
+        <v>10.27253259851824</v>
       </c>
       <c r="R157" t="n">
-        <v>0</v>
+        <v>18.30419929058286</v>
       </c>
       <c r="S157" t="n">
-        <v>0</v>
+        <v>13.21534335010963</v>
       </c>
       <c r="T157" t="n">
-        <v>0</v>
+        <v>9.736156513208464</v>
       </c>
       <c r="U157" t="n">
-        <v>0</v>
+        <v>13.47772597757203</v>
       </c>
       <c r="V157" t="n">
-        <v>0</v>
+        <v>12.6444695784935</v>
       </c>
       <c r="W157" t="n">
-        <v>0</v>
+        <v>8.716918720857908</v>
       </c>
       <c r="X157" t="n">
-        <v>0</v>
+        <v>8.433442461785949</v>
       </c>
       <c r="Y157" t="n">
-        <v>0</v>
+        <v>22.03877397904697</v>
       </c>
       <c r="Z157" t="n">
-        <v>0</v>
+        <v>27.45176556710665</v>
       </c>
       <c r="AA157" t="n">
-        <v>0</v>
+        <v>19.52382849423921</v>
       </c>
       <c r="AB157" t="n">
-        <v>0</v>
+        <v>25.1016460438134</v>
       </c>
       <c r="AC157" t="n">
-        <v>0</v>
+        <v>25.68482399765799</v>
       </c>
       <c r="AD157" t="n">
-        <v>0</v>
+        <v>23.31910619994428</v>
       </c>
       <c r="AE157" t="n">
-        <v>0</v>
+        <v>16.00449981993831</v>
       </c>
       <c r="AF157" t="n">
-        <v>0</v>
+        <v>23.83563332840804</v>
       </c>
       <c r="AG157" t="n">
-        <v>0</v>
+        <v>27.41368505443172</v>
       </c>
       <c r="AH157" t="n">
-        <v>0</v>
+        <v>29.60410192888608</v>
       </c>
       <c r="AI157" t="n">
-        <v>0</v>
+        <v>30.49475565169199</v>
       </c>
       <c r="AJ157" t="n">
-        <v>0</v>
+        <v>36.38708677505301</v>
       </c>
       <c r="AK157" t="n">
-        <v>0</v>
+        <v>33.04929035686938</v>
       </c>
       <c r="AL157" t="n">
-        <v>0</v>
+        <v>34.95997970608689</v>
       </c>
       <c r="AM157" t="n">
-        <v>0</v>
+        <v>36.64814267347331</v>
       </c>
       <c r="AN157" t="n">
-        <v>0</v>
+        <v>33.99255103187546</v>
       </c>
       <c r="AO157" t="n">
-        <v>0</v>
+        <v>0.05781332453997368</v>
       </c>
       <c r="AP157" t="n">
-        <v>0</v>
+        <v>0.04828844242985908</v>
       </c>
       <c r="AQ157" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR157" t="inlineStr">
+        <v>-0.07246183429426611</v>
+      </c>
+      <c r="AR157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX157" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Amendoim</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>0.7945377799145824</v>
+      </c>
+      <c r="D158" t="n">
+        <v>0.6393490004206696</v>
+      </c>
+      <c r="E158" t="n">
+        <v>0.7148228810105807</v>
+      </c>
+      <c r="F158" t="n">
+        <v>0.5782777842028339</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0.7100811857744033</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0.6636224684143889</v>
+      </c>
+      <c r="I158" t="n">
+        <v>0.5933699172320539</v>
+      </c>
+      <c r="J158" t="n">
+        <v>0.567242462146789</v>
+      </c>
+      <c r="K158" t="n">
+        <v>0.5958236692145109</v>
+      </c>
+      <c r="L158" t="n">
+        <v>0.640097591727525</v>
+      </c>
+      <c r="M158" t="n">
+        <v>0.7846386412051261</v>
+      </c>
+      <c r="N158" t="n">
+        <v>0.8725477022628461</v>
+      </c>
+      <c r="O158" t="n">
+        <v>0.6256360402001876</v>
+      </c>
+      <c r="P158" t="n">
+        <v>0.7930853519947677</v>
+      </c>
+      <c r="Q158" t="n">
+        <v>0.9243166140760807</v>
+      </c>
+      <c r="R158" t="n">
+        <v>1.065899876618963</v>
+      </c>
+      <c r="S158" t="n">
+        <v>1.119133814317507</v>
+      </c>
+      <c r="T158" t="n">
+        <v>0.8483498730618763</v>
+      </c>
+      <c r="U158" t="n">
+        <v>1.069928735683675</v>
+      </c>
+      <c r="V158" t="n">
+        <v>1.526555778199134</v>
+      </c>
+      <c r="W158" t="n">
+        <v>0.936916219731059</v>
+      </c>
+      <c r="X158" t="n">
+        <v>0.9025652066777592</v>
+      </c>
+      <c r="Y158" t="n">
+        <v>1.237648310027384</v>
+      </c>
+      <c r="Z158" t="n">
+        <v>1.387206997520059</v>
+      </c>
+      <c r="AA158" t="n">
+        <v>1.708390523027945</v>
+      </c>
+      <c r="AB158" t="n">
+        <v>1.929085433904312</v>
+      </c>
+      <c r="AC158" t="n">
+        <v>2.064149599124498</v>
+      </c>
+      <c r="AD158" t="n">
+        <v>2.318660669992012</v>
+      </c>
+      <c r="AE158" t="n">
+        <v>2.391750794249524</v>
+      </c>
+      <c r="AF158" t="n">
+        <v>2.16166629290305</v>
+      </c>
+      <c r="AG158" t="n">
+        <v>2.51471797829909</v>
+      </c>
+      <c r="AH158" t="n">
+        <v>3.470709185094231</v>
+      </c>
+      <c r="AI158" t="n">
+        <v>3.177822383771538</v>
+      </c>
+      <c r="AJ158" t="n">
+        <v>3.737047972751685</v>
+      </c>
+      <c r="AK158" t="n">
+        <v>4.759001014100185</v>
+      </c>
+      <c r="AL158" t="n">
+        <v>4.48906928636028</v>
+      </c>
+      <c r="AM158" t="n">
+        <v>6.389002085474205</v>
+      </c>
+      <c r="AN158" t="n">
+        <v>5.303762248943634</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>-0.05672025009873682</v>
+      </c>
+      <c r="AP158" t="n">
+        <v>0.4232353474442323</v>
+      </c>
+      <c r="AQ158" t="n">
+        <v>-0.1698606170434552</v>
+      </c>
+      <c r="AR158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX158" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Arroz</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>23.97712593440176</v>
+      </c>
+      <c r="D159" t="n">
+        <v>19.52303099156082</v>
+      </c>
+      <c r="E159" t="n">
+        <v>28.5819992849513</v>
+      </c>
+      <c r="F159" t="n">
+        <v>24.13036357386338</v>
+      </c>
+      <c r="G159" t="n">
+        <v>24.32367035021287</v>
+      </c>
+      <c r="H159" t="n">
+        <v>23.16367754108411</v>
+      </c>
+      <c r="I159" t="n">
+        <v>20.29491524923262</v>
+      </c>
+      <c r="J159" t="n">
+        <v>16.47076896256763</v>
+      </c>
+      <c r="K159" t="n">
+        <v>16.39613088812105</v>
+      </c>
+      <c r="L159" t="n">
+        <v>18.22692912871142</v>
+      </c>
+      <c r="M159" t="n">
+        <v>24.6319316435051</v>
+      </c>
+      <c r="N159" t="n">
+        <v>17.99855706161759</v>
+      </c>
+      <c r="O159" t="n">
+        <v>17.61073601566606</v>
+      </c>
+      <c r="P159" t="n">
+        <v>21.09885733867861</v>
+      </c>
+      <c r="Q159" t="n">
+        <v>25.49795217231257</v>
+      </c>
+      <c r="R159" t="n">
+        <v>32.45895293478068</v>
+      </c>
+      <c r="S159" t="n">
+        <v>23.67805042374113</v>
+      </c>
+      <c r="T159" t="n">
+        <v>18.72225435554233</v>
+      </c>
+      <c r="U159" t="n">
+        <v>18.79062222642287</v>
+      </c>
+      <c r="V159" t="n">
+        <v>24.14187186154977</v>
+      </c>
+      <c r="W159" t="n">
+        <v>25.79552987311025</v>
+      </c>
+      <c r="X159" t="n">
+        <v>19.99360443907264</v>
+      </c>
+      <c r="Y159" t="n">
+        <v>19.62315987297246</v>
+      </c>
+      <c r="Z159" t="n">
+        <v>17.65553312599289</v>
+      </c>
+      <c r="AA159" t="n">
+        <v>21.42368472690845</v>
+      </c>
+      <c r="AB159" t="n">
+        <v>21.97820886591494</v>
+      </c>
+      <c r="AC159" t="n">
+        <v>20.45289746775909</v>
+      </c>
+      <c r="AD159" t="n">
+        <v>18.72422350491182</v>
+      </c>
+      <c r="AE159" t="n">
+        <v>20.43854032178158</v>
+      </c>
+      <c r="AF159" t="n">
+        <v>17.03008232077562</v>
+      </c>
+      <c r="AG159" t="n">
+        <v>16.08664685735343</v>
+      </c>
+      <c r="AH159" t="n">
+        <v>22.1839520357732</v>
+      </c>
+      <c r="AI159" t="n">
+        <v>22.2077833774409</v>
+      </c>
+      <c r="AJ159" t="n">
+        <v>17.81608440573764</v>
+      </c>
+      <c r="AK159" t="n">
+        <v>22.07732607264471</v>
+      </c>
+      <c r="AL159" t="n">
+        <v>25.59568683559726</v>
+      </c>
+      <c r="AM159" t="n">
+        <v>21.39455205773806</v>
+      </c>
+      <c r="AN159" t="n">
+        <v>15.0561629758475</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>0.1593653484745163</v>
+      </c>
+      <c r="AP159" t="n">
+        <v>-0.1641344811273615</v>
+      </c>
+      <c r="AQ159" t="n">
+        <v>-0.2962618270663008</v>
+      </c>
+      <c r="AR159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX159" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Banana</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>15.82647958759992</v>
+      </c>
+      <c r="D160" t="n">
+        <v>17.41262465339798</v>
+      </c>
+      <c r="E160" t="n">
+        <v>15.00773605645964</v>
+      </c>
+      <c r="F160" t="n">
+        <v>12.0874380721632</v>
+      </c>
+      <c r="G160" t="n">
+        <v>12.05042479399742</v>
+      </c>
+      <c r="H160" t="n">
+        <v>17.63250478321047</v>
+      </c>
+      <c r="I160" t="n">
+        <v>23.42443000532142</v>
+      </c>
+      <c r="J160" t="n">
+        <v>16.04781701851268</v>
+      </c>
+      <c r="K160" t="n">
+        <v>13.95215472491511</v>
+      </c>
+      <c r="L160" t="n">
+        <v>14.05942063004349</v>
+      </c>
+      <c r="M160" t="n">
+        <v>14.92851438770587</v>
+      </c>
+      <c r="N160" t="n">
+        <v>12.98059125411589</v>
+      </c>
+      <c r="O160" t="n">
+        <v>12.68062232862005</v>
+      </c>
+      <c r="P160" t="n">
+        <v>12.39215293730417</v>
+      </c>
+      <c r="Q160" t="n">
+        <v>12.90145240528153</v>
+      </c>
+      <c r="R160" t="n">
+        <v>12.76403447962136</v>
+      </c>
+      <c r="S160" t="n">
+        <v>12.99023725475297</v>
+      </c>
+      <c r="T160" t="n">
+        <v>13.46295044310203</v>
+      </c>
+      <c r="U160" t="n">
+        <v>14.23737621033392</v>
+      </c>
+      <c r="V160" t="n">
+        <v>14.34810452849781</v>
+      </c>
+      <c r="W160" t="n">
+        <v>13.80766546802303</v>
+      </c>
+      <c r="X160" t="n">
+        <v>15.44631169695393</v>
+      </c>
+      <c r="Y160" t="n">
+        <v>16.83494513055969</v>
+      </c>
+      <c r="Z160" t="n">
+        <v>15.86694325022315</v>
+      </c>
+      <c r="AA160" t="n">
+        <v>18.05826231670389</v>
+      </c>
+      <c r="AB160" t="n">
+        <v>19.08263304031061</v>
+      </c>
+      <c r="AC160" t="n">
+        <v>18.69336538206326</v>
+      </c>
+      <c r="AD160" t="n">
+        <v>27.52646090274765</v>
+      </c>
+      <c r="AE160" t="n">
+        <v>20.18370916868203</v>
+      </c>
+      <c r="AF160" t="n">
+        <v>17.48362182338888</v>
+      </c>
+      <c r="AG160" t="n">
+        <v>20.13753846820438</v>
+      </c>
+      <c r="AH160" t="n">
+        <v>15.5797162450912</v>
+      </c>
+      <c r="AI160" t="n">
+        <v>13.88186190522946</v>
+      </c>
+      <c r="AJ160" t="n">
+        <v>16.59323832271768</v>
+      </c>
+      <c r="AK160" t="n">
+        <v>19.06679559403977</v>
+      </c>
+      <c r="AL160" t="n">
+        <v>22.76300619379453</v>
+      </c>
+      <c r="AM160" t="n">
+        <v>21.8999816795937</v>
+      </c>
+      <c r="AN160" t="n">
+        <v>22.26604927622303</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>0.1938558884488268</v>
+      </c>
+      <c r="AP160" t="n">
+        <v>-0.03791346832019493</v>
+      </c>
+      <c r="AQ160" t="n">
+        <v>0.01671542935446535</v>
+      </c>
+      <c r="AR160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX160" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Batata - inglesa</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>7.873923153838367</v>
+      </c>
+      <c r="D161" t="n">
+        <v>9.832416915716401</v>
+      </c>
+      <c r="E161" t="n">
+        <v>7.226342238085628</v>
+      </c>
+      <c r="F161" t="n">
+        <v>7.711647703568795</v>
+      </c>
+      <c r="G161" t="n">
+        <v>5.85844706257768</v>
+      </c>
+      <c r="H161" t="n">
+        <v>11.51142002655004</v>
+      </c>
+      <c r="I161" t="n">
+        <v>8.724092638185802</v>
+      </c>
+      <c r="J161" t="n">
+        <v>5.999980415457125</v>
+      </c>
+      <c r="K161" t="n">
+        <v>7.256280050699178</v>
+      </c>
+      <c r="L161" t="n">
+        <v>9.302815604167467</v>
+      </c>
+      <c r="M161" t="n">
+        <v>6.46806016078016</v>
+      </c>
+      <c r="N161" t="n">
+        <v>6.426683237611916</v>
+      </c>
+      <c r="O161" t="n">
+        <v>9.447271961824764</v>
+      </c>
+      <c r="P161" t="n">
+        <v>8.244245643309387</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>7.805908211849157</v>
+      </c>
+      <c r="R161" t="n">
+        <v>6.372574263214507</v>
+      </c>
+      <c r="S161" t="n">
+        <v>7.439944986444956</v>
+      </c>
+      <c r="T161" t="n">
+        <v>6.997795586467027</v>
+      </c>
+      <c r="U161" t="n">
+        <v>7.552352323835244</v>
+      </c>
+      <c r="V161" t="n">
+        <v>7.66903700557802</v>
+      </c>
+      <c r="W161" t="n">
+        <v>9.506018776372663</v>
+      </c>
+      <c r="X161" t="n">
+        <v>10.11688326462882</v>
+      </c>
+      <c r="Y161" t="n">
+        <v>8.349987185636266</v>
+      </c>
+      <c r="Z161" t="n">
+        <v>6.582174030975265</v>
+      </c>
+      <c r="AA161" t="n">
+        <v>9.841082072449895</v>
+      </c>
+      <c r="AB161" t="n">
+        <v>11.4550253186669</v>
+      </c>
+      <c r="AC161" t="n">
+        <v>11.31882613044761</v>
+      </c>
+      <c r="AD161" t="n">
+        <v>13.63842152819428</v>
+      </c>
+      <c r="AE161" t="n">
+        <v>7.319367749631507</v>
+      </c>
+      <c r="AF161" t="n">
+        <v>6.991553866066427</v>
+      </c>
+      <c r="AG161" t="n">
+        <v>13.08299105025496</v>
+      </c>
+      <c r="AH161" t="n">
+        <v>10.50305864892995</v>
+      </c>
+      <c r="AI161" t="n">
+        <v>9.689062778322093</v>
+      </c>
+      <c r="AJ161" t="n">
+        <v>11.84618416417077</v>
+      </c>
+      <c r="AK161" t="n">
+        <v>12.74567710970222</v>
+      </c>
+      <c r="AL161" t="n">
+        <v>19.99487943684498</v>
+      </c>
+      <c r="AM161" t="n">
+        <v>9.263588771670147</v>
+      </c>
+      <c r="AN161" t="n">
+        <v>12.79780803869605</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>0.5687577258351024</v>
+      </c>
+      <c r="AP161" t="n">
+        <v>-0.5367019440687428</v>
+      </c>
+      <c r="AQ161" t="n">
+        <v>0.3815172881847082</v>
+      </c>
+      <c r="AR161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX161" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Cacau</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>4.828479928109874</v>
+      </c>
+      <c r="D162" t="n">
+        <v>3.81444503105048</v>
+      </c>
+      <c r="E162" t="n">
+        <v>4.10903786724788</v>
+      </c>
+      <c r="F162" t="n">
+        <v>3.787933861047644</v>
+      </c>
+      <c r="G162" t="n">
+        <v>4.021078729501228</v>
+      </c>
+      <c r="H162" t="n">
+        <v>3.593339621489504</v>
+      </c>
+      <c r="I162" t="n">
+        <v>3.047667299002346</v>
+      </c>
+      <c r="J162" t="n">
+        <v>2.533121711332348</v>
+      </c>
+      <c r="K162" t="n">
+        <v>3.411726899114446</v>
+      </c>
+      <c r="L162" t="n">
+        <v>3.687220329829172</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2.69920631628922</v>
+      </c>
+      <c r="N162" t="n">
+        <v>1.935473917521459</v>
+      </c>
+      <c r="O162" t="n">
+        <v>2.514264155831278</v>
+      </c>
+      <c r="P162" t="n">
+        <v>4.75390567276609</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>3.954175308657773</v>
+      </c>
+      <c r="R162" t="n">
+        <v>3.242492900540748</v>
+      </c>
+      <c r="S162" t="n">
+        <v>2.726669985924956</v>
+      </c>
+      <c r="T162" t="n">
+        <v>2.41666680089266</v>
+      </c>
+      <c r="U162" t="n">
+        <v>2.571552737510073</v>
+      </c>
+      <c r="V162" t="n">
+        <v>2.911207315544917</v>
+      </c>
+      <c r="W162" t="n">
+        <v>3.744726279003908</v>
+      </c>
+      <c r="X162" t="n">
+        <v>3.773736566911954</v>
+      </c>
+      <c r="Y162" t="n">
+        <v>3.222319846539278</v>
+      </c>
+      <c r="Z162" t="n">
+        <v>2.974302592205812</v>
+      </c>
+      <c r="AA162" t="n">
+        <v>2.844788709860981</v>
+      </c>
+      <c r="AB162" t="n">
+        <v>2.320328027047023</v>
+      </c>
+      <c r="AC162" t="n">
+        <v>2.692569179957542</v>
+      </c>
+      <c r="AD162" t="n">
+        <v>3.510821650532424</v>
+      </c>
+      <c r="AE162" t="n">
+        <v>2.555710468569171</v>
+      </c>
+      <c r="AF162" t="n">
+        <v>3.464585592577869</v>
+      </c>
+      <c r="AG162" t="n">
+        <v>3.638723197880027</v>
+      </c>
+      <c r="AH162" t="n">
+        <v>4.570239776819784</v>
+      </c>
+      <c r="AI162" t="n">
+        <v>4.678540776558493</v>
+      </c>
+      <c r="AJ162" t="n">
+        <v>3.4568279274414</v>
+      </c>
+      <c r="AK162" t="n">
+        <v>4.46838674091329</v>
+      </c>
+      <c r="AL162" t="n">
+        <v>11.36638430421513</v>
+      </c>
+      <c r="AM162" t="n">
+        <v>11.90191643613502</v>
+      </c>
+      <c r="AN162" t="n">
+        <v>5.015201538842655</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>1.543733334481241</v>
+      </c>
+      <c r="AP162" t="n">
+        <v>0.04711543421255748</v>
+      </c>
+      <c r="AQ162" t="n">
+        <v>-0.5786223533198265</v>
+      </c>
+      <c r="AR162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX162" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Café</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K163" t="n">
+        <v>37.18645671032893</v>
+      </c>
+      <c r="L163" t="n">
+        <v>37.94753670150229</v>
+      </c>
+      <c r="M163" t="n">
+        <v>36.79181364286369</v>
+      </c>
+      <c r="N163" t="n">
+        <v>33.80544326864866</v>
+      </c>
+      <c r="O163" t="n">
+        <v>21.02974776569779</v>
+      </c>
+      <c r="P163" t="n">
+        <v>29.26273096150227</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>24.28065183310744</v>
+      </c>
+      <c r="R163" t="n">
+        <v>34.42135965074291</v>
+      </c>
+      <c r="S163" t="n">
+        <v>36.48194567261424</v>
+      </c>
+      <c r="T163" t="n">
+        <v>38.396405562492</v>
+      </c>
+      <c r="U163" t="n">
+        <v>32.20245491478835</v>
+      </c>
+      <c r="V163" t="n">
+        <v>37.13612531883352</v>
+      </c>
+      <c r="W163" t="n">
+        <v>32.17454314294494</v>
+      </c>
+      <c r="X163" t="n">
+        <v>42.89144468869854</v>
+      </c>
+      <c r="Y163" t="n">
+        <v>49.60299268326833</v>
+      </c>
+      <c r="Z163" t="n">
+        <v>45.46756453784501</v>
+      </c>
+      <c r="AA163" t="n">
+        <v>32.11806644965608</v>
+      </c>
+      <c r="AB163" t="n">
+        <v>38.47271152512142</v>
+      </c>
+      <c r="AC163" t="n">
+        <v>38.33360425332103</v>
+      </c>
+      <c r="AD163" t="n">
+        <v>45.7414906196363</v>
+      </c>
+      <c r="AE163" t="n">
+        <v>39.0246360493989</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>42.96783135184464</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>31.89475777228168</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>45.59577645008974</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>47.05169756347911</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>58.7806473465758</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>53.69846632361509</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>80.99840900448309</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>118.0410830382954</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>104.3715126222963</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>0.5083933406280963</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>0.4573259461400296</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>-0.1158034987832529</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX163" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Café arábica</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K164" t="n">
+        <v>37.18645671032893</v>
+      </c>
+      <c r="L164" t="n">
+        <v>37.94753670150229</v>
+      </c>
+      <c r="M164" t="n">
+        <v>36.79181364286369</v>
+      </c>
+      <c r="N164" t="n">
+        <v>33.80544326864866</v>
+      </c>
+      <c r="O164" t="n">
+        <v>21.02974776569779</v>
+      </c>
+      <c r="P164" t="n">
+        <v>29.26273096150227</v>
+      </c>
+      <c r="Q164" t="n">
+        <v>24.28065183310744</v>
+      </c>
+      <c r="R164" t="n">
+        <v>34.42135965074291</v>
+      </c>
+      <c r="S164" t="n">
+        <v>36.48194567261424</v>
+      </c>
+      <c r="T164" t="n">
+        <v>38.396405562492</v>
+      </c>
+      <c r="U164" t="n">
+        <v>32.20245491478835</v>
+      </c>
+      <c r="V164" t="n">
+        <v>37.13612531883352</v>
+      </c>
+      <c r="W164" t="n">
+        <v>32.17454314294494</v>
+      </c>
+      <c r="X164" t="n">
+        <v>42.89144468869854</v>
+      </c>
+      <c r="Y164" t="n">
+        <v>42.53594608667589</v>
+      </c>
+      <c r="Z164" t="n">
+        <v>37.05499790288498</v>
+      </c>
+      <c r="AA164" t="n">
+        <v>26.06869652802462</v>
+      </c>
+      <c r="AB164" t="n">
+        <v>31.09343667134787</v>
+      </c>
+      <c r="AC164" t="n">
+        <v>31.08439605751299</v>
+      </c>
+      <c r="AD164" t="n">
+        <v>39.49155309196206</v>
+      </c>
+      <c r="AE164" t="n">
+        <v>30.2861462543295</v>
+      </c>
+      <c r="AF164" t="n">
+        <v>34.4216396176578</v>
+      </c>
+      <c r="AG164" t="n">
+        <v>24.38768428414872</v>
+      </c>
+      <c r="AH164" t="n">
+        <v>37.99610531248634</v>
+      </c>
+      <c r="AI164" t="n">
+        <v>35.50837060146146</v>
+      </c>
+      <c r="AJ164" t="n">
+        <v>44.71793623811048</v>
+      </c>
+      <c r="AK164" t="n">
+        <v>40.91864585174653</v>
+      </c>
+      <c r="AL164" t="n">
+        <v>58.65597307057337</v>
+      </c>
+      <c r="AM164" t="n">
+        <v>85.32787433745956</v>
+      </c>
+      <c r="AN164" t="n">
+        <v>81.73991025067647</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>0.4334778644213066</v>
+      </c>
+      <c r="AP164" t="n">
+        <v>0.4547175653329498</v>
+      </c>
+      <c r="AQ164" t="n">
+        <v>-0.0420491441353994</v>
+      </c>
+      <c r="AR164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX164" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Café conilon</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y165" t="n">
+        <v>7.067046596592437</v>
+      </c>
+      <c r="Z165" t="n">
+        <v>8.412566634960022</v>
+      </c>
+      <c r="AA165" t="n">
+        <v>6.049369921631456</v>
+      </c>
+      <c r="AB165" t="n">
+        <v>7.379274853773555</v>
+      </c>
+      <c r="AC165" t="n">
+        <v>7.249208195808044</v>
+      </c>
+      <c r="AD165" t="n">
+        <v>6.249937527674237</v>
+      </c>
+      <c r="AE165" t="n">
+        <v>8.738489795069407</v>
+      </c>
+      <c r="AF165" t="n">
+        <v>8.546191734186829</v>
+      </c>
+      <c r="AG165" t="n">
+        <v>7.507073488132954</v>
+      </c>
+      <c r="AH165" t="n">
+        <v>7.599671137603396</v>
+      </c>
+      <c r="AI165" t="n">
+        <v>11.54332696201766</v>
+      </c>
+      <c r="AJ165" t="n">
+        <v>14.06271110846532</v>
+      </c>
+      <c r="AK165" t="n">
+        <v>12.77982047186857</v>
+      </c>
+      <c r="AL165" t="n">
+        <v>22.34243593390973</v>
+      </c>
+      <c r="AM165" t="n">
+        <v>32.71320870083586</v>
+      </c>
+      <c r="AN165" t="n">
+        <v>22.63160237161985</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>0.7482589824396011</v>
+      </c>
+      <c r="AP165" t="n">
+        <v>0.4641737721707471</v>
+      </c>
+      <c r="AQ165" t="n">
+        <v>-0.3081815184017218</v>
+      </c>
+      <c r="AR165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX165" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Cana-de-açúcar</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>35.5366262038472</v>
+      </c>
+      <c r="D166" t="n">
+        <v>38.03222274768355</v>
+      </c>
+      <c r="E166" t="n">
+        <v>38.08435037702476</v>
+      </c>
+      <c r="F166" t="n">
+        <v>40.78782126891084</v>
+      </c>
+      <c r="G166" t="n">
+        <v>34.50952368442999</v>
+      </c>
+      <c r="H166" t="n">
+        <v>40.81636981285749</v>
+      </c>
+      <c r="I166" t="n">
+        <v>38.85492269286053</v>
+      </c>
+      <c r="J166" t="n">
+        <v>44.29526598908343</v>
+      </c>
+      <c r="K166" t="n">
+        <v>47.25847609991794</v>
+      </c>
+      <c r="L166" t="n">
+        <v>47.99514205600853</v>
+      </c>
+      <c r="M166" t="n">
+        <v>37.0968675073117</v>
+      </c>
+      <c r="N166" t="n">
+        <v>39.51230490990262</v>
+      </c>
+      <c r="O166" t="n">
+        <v>51.08623416012636</v>
+      </c>
+      <c r="P166" t="n">
+        <v>49.35259750501005</v>
+      </c>
+      <c r="Q166" t="n">
+        <v>50.21545511522251</v>
+      </c>
+      <c r="R166" t="n">
+        <v>45.54894825426038</v>
+      </c>
+      <c r="S166" t="n">
+        <v>48.75849117981959</v>
+      </c>
+      <c r="T166" t="n">
+        <v>66.94927364314901</v>
+      </c>
+      <c r="U166" t="n">
+        <v>69.32964793950033</v>
+      </c>
+      <c r="V166" t="n">
+        <v>62.7230682896999</v>
+      </c>
+      <c r="W166" t="n">
+        <v>76.74374997511678</v>
+      </c>
+      <c r="X166" t="n">
+        <v>86.12100007778076</v>
+      </c>
+      <c r="Y166" t="n">
+        <v>103.5771430984477</v>
+      </c>
+      <c r="Z166" t="n">
+        <v>111.0340089142601</v>
+      </c>
+      <c r="AA166" t="n">
+        <v>115.493819478831</v>
+      </c>
+      <c r="AB166" t="n">
+        <v>103.7029676812439</v>
+      </c>
+      <c r="AC166" t="n">
+        <v>98.16501751867182</v>
+      </c>
+      <c r="AD166" t="n">
+        <v>103.1282027640163</v>
+      </c>
+      <c r="AE166" t="n">
+        <v>126.2104522475032</v>
+      </c>
+      <c r="AF166" t="n">
+        <v>105.1060721058168</v>
+      </c>
+      <c r="AG166" t="n">
+        <v>94.95707154138994</v>
+      </c>
+      <c r="AH166" t="n">
+        <v>92.01098426144698</v>
+      </c>
+      <c r="AI166" t="n">
+        <v>96.61047257295598</v>
+      </c>
+      <c r="AJ166" t="n">
+        <v>104.3961420805096</v>
+      </c>
+      <c r="AK166" t="n">
+        <v>123.6589902770076</v>
+      </c>
+      <c r="AL166" t="n">
+        <v>123.6053094967391</v>
+      </c>
+      <c r="AM166" t="n">
+        <v>120.2384727865754</v>
+      </c>
+      <c r="AN166" t="n">
+        <v>108.7703502812351</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>-0.0004341033365083957</v>
+      </c>
+      <c r="AP166" t="n">
+        <v>-0.02723860911696974</v>
+      </c>
+      <c r="AQ166" t="n">
+        <v>-0.09537814511081055</v>
+      </c>
+      <c r="AR166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX166" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Cebola</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>3.275374984626241</v>
+      </c>
+      <c r="D167" t="n">
+        <v>5.630795953433674</v>
+      </c>
+      <c r="E167" t="n">
+        <v>2.729604822426484</v>
+      </c>
+      <c r="F167" t="n">
+        <v>4.813445917904518</v>
+      </c>
+      <c r="G167" t="n">
+        <v>2.487694282860965</v>
+      </c>
+      <c r="H167" t="n">
+        <v>3.536604630378269</v>
+      </c>
+      <c r="I167" t="n">
+        <v>4.194705169061153</v>
+      </c>
+      <c r="J167" t="n">
+        <v>1.851173690220847</v>
+      </c>
+      <c r="K167" t="n">
+        <v>3.641474899558861</v>
+      </c>
+      <c r="L167" t="n">
+        <v>3.007410062585782</v>
+      </c>
+      <c r="M167" t="n">
+        <v>3.003999474210174</v>
+      </c>
+      <c r="N167" t="n">
+        <v>3.056917741174059</v>
+      </c>
+      <c r="O167" t="n">
+        <v>3.092353743629732</v>
+      </c>
+      <c r="P167" t="n">
+        <v>3.291269957816048</v>
+      </c>
+      <c r="Q167" t="n">
+        <v>2.934915524577603</v>
+      </c>
+      <c r="R167" t="n">
+        <v>3.369163535329983</v>
+      </c>
+      <c r="S167" t="n">
+        <v>2.466112439996339</v>
+      </c>
+      <c r="T167" t="n">
+        <v>2.346537432199542</v>
+      </c>
+      <c r="U167" t="n">
+        <v>2.515432855285505</v>
+      </c>
+      <c r="V167" t="n">
+        <v>3.977190097305134</v>
+      </c>
+      <c r="W167" t="n">
+        <v>3.612835519772402</v>
+      </c>
+      <c r="X167" t="n">
+        <v>5.940264837678952</v>
+      </c>
+      <c r="Y167" t="n">
+        <v>2.341245774903024</v>
+      </c>
+      <c r="Z167" t="n">
+        <v>3.04365025385723</v>
+      </c>
+      <c r="AA167" t="n">
+        <v>6.745013813359926</v>
+      </c>
+      <c r="AB167" t="n">
+        <v>7.888778717653266</v>
+      </c>
+      <c r="AC167" t="n">
+        <v>5.968758978299473</v>
+      </c>
+      <c r="AD167" t="n">
+        <v>6.803509159440756</v>
+      </c>
+      <c r="AE167" t="n">
+        <v>3.439931015794218</v>
+      </c>
+      <c r="AF167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX167" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Feijão</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>20.58973230539203</v>
+      </c>
+      <c r="D168" t="n">
+        <v>17.13560662637633</v>
+      </c>
+      <c r="E168" t="n">
+        <v>18.62320017400801</v>
+      </c>
+      <c r="F168" t="n">
+        <v>17.91398286370454</v>
+      </c>
+      <c r="G168" t="n">
+        <v>18.70773558118682</v>
+      </c>
+      <c r="H168" t="n">
+        <v>25.48494218400223</v>
+      </c>
+      <c r="I168" t="n">
+        <v>15.0238956810353</v>
+      </c>
+      <c r="J168" t="n">
+        <v>13.75857446954655</v>
+      </c>
+      <c r="K168" t="n">
+        <v>14.28348360985209</v>
+      </c>
+      <c r="L168" t="n">
+        <v>18.78339787373221</v>
+      </c>
+      <c r="M168" t="n">
+        <v>15.74062884201532</v>
+      </c>
+      <c r="N168" t="n">
+        <v>12.22695987600364</v>
+      </c>
+      <c r="O168" t="n">
+        <v>13.72652880302132</v>
+      </c>
+      <c r="P168" t="n">
+        <v>18.22359006041373</v>
+      </c>
+      <c r="Q168" t="n">
+        <v>18.8470109878911</v>
+      </c>
+      <c r="R168" t="n">
+        <v>13.19180714313502</v>
+      </c>
+      <c r="S168" t="n">
+        <v>14.34563590674995</v>
+      </c>
+      <c r="T168" t="n">
+        <v>14.72591465251581</v>
+      </c>
+      <c r="U168" t="n">
+        <v>14.08543088348054</v>
+      </c>
+      <c r="V168" t="n">
+        <v>25.2490488626377</v>
+      </c>
+      <c r="W168" t="n">
+        <v>17.1448218871095</v>
+      </c>
+      <c r="X168" t="n">
+        <v>15.47658951849971</v>
+      </c>
+      <c r="Y168" t="n">
+        <v>15.20145643474578</v>
+      </c>
+      <c r="Z168" t="n">
+        <v>17.89641148477933</v>
+      </c>
+      <c r="AA168" t="n">
+        <v>18.75413899413824</v>
+      </c>
+      <c r="AB168" t="n">
+        <v>16.99595838538736</v>
+      </c>
+      <c r="AC168" t="n">
+        <v>16.2346690077176</v>
+      </c>
+      <c r="AD168" t="n">
+        <v>20.97714611298414</v>
+      </c>
+      <c r="AE168" t="n">
+        <v>15.37465837547072</v>
+      </c>
+      <c r="AF168" t="n">
+        <v>9.945904909269906</v>
+      </c>
+      <c r="AG168" t="n">
+        <v>15.59100328050554</v>
+      </c>
+      <c r="AH168" t="n">
+        <v>17.2641613367243</v>
+      </c>
+      <c r="AI168" t="n">
+        <v>14.68595369543188</v>
+      </c>
+      <c r="AJ168" t="n">
+        <v>16.17228000765938</v>
+      </c>
+      <c r="AK168" t="n">
+        <v>16.25637399209208</v>
+      </c>
+      <c r="AL168" t="n">
+        <v>15.21241281313839</v>
+      </c>
+      <c r="AM168" t="n">
+        <v>12.0908330347416</v>
+      </c>
+      <c r="AN168" t="n">
+        <v>14.00290453511152</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>-0.06421857540073306</v>
+      </c>
+      <c r="AP168" t="n">
+        <v>-0.2051995181001666</v>
+      </c>
+      <c r="AQ168" t="n">
+        <v>0.1581422466819129</v>
+      </c>
+      <c r="AR168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX168" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Fumo</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>7.028570279034075</v>
+      </c>
+      <c r="D169" t="n">
+        <v>7.302735361718899</v>
+      </c>
+      <c r="E169" t="n">
+        <v>6.677558666228913</v>
+      </c>
+      <c r="F169" t="n">
+        <v>13.54062064988302</v>
+      </c>
+      <c r="G169" t="n">
+        <v>13.64503995193254</v>
+      </c>
+      <c r="H169" t="n">
+        <v>9.317393588740453</v>
+      </c>
+      <c r="I169" t="n">
+        <v>7.668003223610794</v>
+      </c>
+      <c r="J169" t="n">
+        <v>8.912410206637375</v>
+      </c>
+      <c r="K169" t="n">
+        <v>10.01249797258281</v>
+      </c>
+      <c r="L169" t="n">
+        <v>8.442708599068885</v>
+      </c>
+      <c r="M169" t="n">
+        <v>9.869829165525969</v>
+      </c>
+      <c r="N169" t="n">
+        <v>8.28348403584581</v>
+      </c>
+      <c r="O169" t="n">
+        <v>7.995470089961383</v>
+      </c>
+      <c r="P169" t="n">
+        <v>9.303679342641237</v>
+      </c>
+      <c r="Q169" t="n">
+        <v>10.05534804348119</v>
+      </c>
+      <c r="R169" t="n">
+        <v>14.79237809353287</v>
+      </c>
+      <c r="S169" t="n">
+        <v>14.53125707839058</v>
+      </c>
+      <c r="T169" t="n">
+        <v>14.82572083286436</v>
+      </c>
+      <c r="U169" t="n">
+        <v>15.37788629412566</v>
+      </c>
+      <c r="V169" t="n">
+        <v>15.12709255023376</v>
+      </c>
+      <c r="W169" t="n">
+        <v>15.24157740500741</v>
+      </c>
+      <c r="X169" t="n">
+        <v>12.52703856354181</v>
+      </c>
+      <c r="Y169" t="n">
+        <v>12.42251813150957</v>
+      </c>
+      <c r="Z169" t="n">
+        <v>13.28324442018598</v>
+      </c>
+      <c r="AA169" t="n">
+        <v>15.0918898487586</v>
+      </c>
+      <c r="AB169" t="n">
+        <v>15.40318291484484</v>
+      </c>
+      <c r="AC169" t="n">
+        <v>14.89301795366656</v>
+      </c>
+      <c r="AD169" t="n">
+        <v>10.57234612434897</v>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX169" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Laranja</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>25.93565148058164</v>
+      </c>
+      <c r="D170" t="n">
+        <v>26.66776505072974</v>
+      </c>
+      <c r="E170" t="n">
+        <v>24.50097598357725</v>
+      </c>
+      <c r="F170" t="n">
+        <v>23.27055802555351</v>
+      </c>
+      <c r="G170" t="n">
+        <v>19.86048492589633</v>
+      </c>
+      <c r="H170" t="n">
+        <v>23.71781330569742</v>
+      </c>
+      <c r="I170" t="n">
+        <v>25.92417586017866</v>
+      </c>
+      <c r="J170" t="n">
+        <v>17.81424514592475</v>
+      </c>
+      <c r="K170" t="n">
+        <v>22.02457574623351</v>
+      </c>
+      <c r="L170" t="n">
+        <v>24.04117896172952</v>
+      </c>
+      <c r="M170" t="n">
+        <v>23.74067202021723</v>
+      </c>
+      <c r="N170" t="n">
+        <v>15.07752825147295</v>
+      </c>
+      <c r="O170" t="n">
+        <v>27.04907673938617</v>
+      </c>
+      <c r="P170" t="n">
+        <v>32.71465698040867</v>
+      </c>
+      <c r="Q170" t="n">
+        <v>27.33964301373879</v>
+      </c>
+      <c r="R170" t="n">
+        <v>24.42701511035932</v>
+      </c>
+      <c r="S170" t="n">
+        <v>23.32837206516358</v>
+      </c>
+      <c r="T170" t="n">
+        <v>27.81787136620632</v>
+      </c>
+      <c r="U170" t="n">
+        <v>26.21523807756919</v>
+      </c>
+      <c r="V170" t="n">
+        <v>26.98109328569232</v>
+      </c>
+      <c r="W170" t="n">
+        <v>23.63843861890748</v>
+      </c>
+      <c r="X170" t="n">
+        <v>30.68332332244504</v>
+      </c>
+      <c r="Y170" t="n">
+        <v>34.10559041699135</v>
+      </c>
+      <c r="Z170" t="n">
+        <v>20.24211294542746</v>
+      </c>
+      <c r="AA170" t="n">
+        <v>21.88725035240047</v>
+      </c>
+      <c r="AB170" t="n">
+        <v>26.40147176132123</v>
+      </c>
+      <c r="AC170" t="n">
+        <v>22.3264760569226</v>
+      </c>
+      <c r="AD170" t="n">
+        <v>23.80961593567787</v>
+      </c>
+      <c r="AE170" t="n">
+        <v>26.46418279406719</v>
+      </c>
+      <c r="AF170" t="n">
+        <v>21.46709676550153</v>
+      </c>
+      <c r="AG170" t="n">
+        <v>21.47599470281357</v>
+      </c>
+      <c r="AH170" t="n">
+        <v>19.48112352583118</v>
+      </c>
+      <c r="AI170" t="n">
+        <v>19.05640117886756</v>
+      </c>
+      <c r="AJ170" t="n">
+        <v>18.31579521816015</v>
+      </c>
+      <c r="AK170" t="n">
+        <v>22.45790066834323</v>
+      </c>
+      <c r="AL170" t="n">
+        <v>29.0739495325444</v>
+      </c>
+      <c r="AM170" t="n">
+        <v>25.06205368373911</v>
+      </c>
+      <c r="AN170" t="n">
+        <v>15.08134885109032</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>0.2945978327140428</v>
+      </c>
+      <c r="AP170" t="n">
+        <v>-0.1379893655079271</v>
+      </c>
+      <c r="AQ170" t="n">
+        <v>-0.3982397036809684</v>
+      </c>
+      <c r="AR170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX170" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Mamona</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>0.4911993915400256</v>
+      </c>
+      <c r="D171" t="n">
+        <v>0.3340390204857535</v>
+      </c>
+      <c r="E171" t="n">
+        <v>0.2487699762455969</v>
+      </c>
+      <c r="F171" t="n">
+        <v>0.2121083798096426</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0.107633586908349</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0.1257211588238312</v>
+      </c>
+      <c r="I171" t="n">
+        <v>0.07943293666598578</v>
+      </c>
+      <c r="J171" t="n">
+        <v>0.09679714752619178</v>
+      </c>
+      <c r="K171" t="n">
+        <v>0.2023958671899395</v>
+      </c>
+      <c r="L171" t="n">
+        <v>0.03232642739858983</v>
+      </c>
+      <c r="M171" t="n">
+        <v>0.07837493006855696</v>
+      </c>
+      <c r="N171" t="n">
+        <v>0.3290262556346235</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0.2227771875686283</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0.1681789674103819</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0.2273452774507101</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0.4229930056079891</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0.4078693690881715</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0.1871467453237089</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0.2031925966296352</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0.2690747100336116</v>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y171" t="n">
+        <v>0.3592152035556335</v>
+      </c>
+      <c r="Z171" t="n">
+        <v>0.08253389374533697</v>
+      </c>
+      <c r="AA171" t="n">
+        <v>0.03994016060567857</v>
+      </c>
+      <c r="AB171" t="n">
+        <v>0.1151455606996572</v>
+      </c>
+      <c r="AC171" t="n">
+        <v>0.1277706396492719</v>
+      </c>
+      <c r="AD171" t="n">
+        <v>0.08394573254870931</v>
+      </c>
+      <c r="AE171" t="n">
+        <v>0.05091557538148411</v>
+      </c>
+      <c r="AF171" t="n">
+        <v>0.08308805308920246</v>
+      </c>
+      <c r="AG171" t="n">
+        <v>0.10720699415234</v>
+      </c>
+      <c r="AH171" t="n">
+        <v>0.1310357029887741</v>
+      </c>
+      <c r="AI171" t="n">
+        <v>0.1009297997324015</v>
+      </c>
+      <c r="AJ171" t="n">
+        <v>0.1309466974267655</v>
+      </c>
+      <c r="AK171" t="n">
+        <v>0.1119461123278254</v>
+      </c>
+      <c r="AL171" t="n">
+        <v>0.1265486185948952</v>
+      </c>
+      <c r="AM171" t="n">
+        <v>0.1556293856401624</v>
+      </c>
+      <c r="AN171" t="n">
+        <v>0.1257390092111593</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>0.1304422812317731</v>
+      </c>
+      <c r="AP171" t="n">
+        <v>0.2297991662663652</v>
+      </c>
+      <c r="AQ171" t="n">
+        <v>-0.1920612634050612</v>
+      </c>
+      <c r="AR171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX171" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Mandioca</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>15.20703546876999</v>
+      </c>
+      <c r="D172" t="n">
+        <v>13.1880957315023</v>
+      </c>
+      <c r="E172" t="n">
+        <v>14.49295479442239</v>
+      </c>
+      <c r="F172" t="n">
+        <v>15.06847720962709</v>
+      </c>
+      <c r="G172" t="n">
+        <v>13.21605069970672</v>
+      </c>
+      <c r="H172" t="n">
+        <v>11.26497601908084</v>
+      </c>
+      <c r="I172" t="n">
+        <v>17.12856707259589</v>
+      </c>
+      <c r="J172" t="n">
+        <v>12.52323479043104</v>
+      </c>
+      <c r="K172" t="n">
+        <v>13.06349572381499</v>
+      </c>
+      <c r="L172" t="n">
+        <v>11.88653956538539</v>
+      </c>
+      <c r="M172" t="n">
+        <v>12.53626725866223</v>
+      </c>
+      <c r="N172" t="n">
+        <v>11.63517105895611</v>
+      </c>
+      <c r="O172" t="n">
+        <v>9.173461845814861</v>
+      </c>
+      <c r="P172" t="n">
+        <v>9.369794723009983</v>
+      </c>
+      <c r="Q172" t="n">
+        <v>13.1651460899642</v>
+      </c>
+      <c r="R172" t="n">
+        <v>17.35147366428214</v>
+      </c>
+      <c r="S172" t="n">
+        <v>16.22785928418861</v>
+      </c>
+      <c r="T172" t="n">
+        <v>15.5366467871335</v>
+      </c>
+      <c r="U172" t="n">
+        <v>14.47507828425126</v>
+      </c>
+      <c r="V172" t="n">
+        <v>15.53846099506147</v>
+      </c>
+      <c r="W172" t="n">
+        <v>15.53954981041495</v>
+      </c>
+      <c r="X172" t="n">
+        <v>16.219830689951</v>
+      </c>
+      <c r="Y172" t="n">
+        <v>15.39841230291796</v>
+      </c>
+      <c r="Z172" t="n">
+        <v>13.97657671566254</v>
+      </c>
+      <c r="AA172" t="n">
+        <v>14.96189417477702</v>
+      </c>
+      <c r="AB172" t="n">
+        <v>15.95417601598892</v>
+      </c>
+      <c r="AC172" t="n">
+        <v>14.17263511795675</v>
+      </c>
+      <c r="AD172" t="n">
+        <v>11.91152505394113</v>
+      </c>
+      <c r="AE172" t="n">
+        <v>22.3135563614655</v>
+      </c>
+      <c r="AF172" t="n">
+        <v>16.84656837610738</v>
+      </c>
+      <c r="AG172" t="n">
+        <v>13.82186679730026</v>
+      </c>
+      <c r="AH172" t="n">
+        <v>13.75789812939853</v>
+      </c>
+      <c r="AI172" t="n">
+        <v>12.96581329624651</v>
+      </c>
+      <c r="AJ172" t="n">
+        <v>15.29891282013976</v>
+      </c>
+      <c r="AK172" t="n">
+        <v>22.00271751452739</v>
+      </c>
+      <c r="AL172" t="n">
+        <v>19.96934347741175</v>
+      </c>
+      <c r="AM172" t="n">
+        <v>20.35406368042693</v>
+      </c>
+      <c r="AN172" t="n">
+        <v>21.67267841355875</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>-0.09241467722216989</v>
+      </c>
+      <c r="AP172" t="n">
+        <v>0.01926554087520937</v>
+      </c>
+      <c r="AQ172" t="n">
+        <v>0.06478385612991122</v>
+      </c>
+      <c r="AR172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX172" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Milho</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>43.07795978570613</v>
+      </c>
+      <c r="D173" t="n">
+        <v>38.59472144637416</v>
+      </c>
+      <c r="E173" t="n">
+        <v>42.18906397458004</v>
+      </c>
+      <c r="F173" t="n">
+        <v>50.36834990730381</v>
+      </c>
+      <c r="G173" t="n">
+        <v>51.565411225092</v>
+      </c>
+      <c r="H173" t="n">
+        <v>44.52318057433298</v>
+      </c>
+      <c r="I173" t="n">
+        <v>41.75117298482032</v>
+      </c>
+      <c r="J173" t="n">
+        <v>39.37684349534298</v>
+      </c>
+      <c r="K173" t="n">
+        <v>35.15443522545007</v>
+      </c>
+      <c r="L173" t="n">
+        <v>34.86125380309998</v>
+      </c>
+      <c r="M173" t="n">
+        <v>40.45246592688529</v>
+      </c>
+      <c r="N173" t="n">
+        <v>42.28560066961791</v>
+      </c>
+      <c r="O173" t="n">
+        <v>40.08410847103067</v>
+      </c>
+      <c r="P173" t="n">
+        <v>48.55076832584611</v>
+      </c>
+      <c r="Q173" t="n">
+        <v>64.5432347678735</v>
+      </c>
+      <c r="R173" t="n">
+        <v>48.73076732237823</v>
+      </c>
+      <c r="S173" t="n">
+        <v>36.83265931563229</v>
+      </c>
+      <c r="T173" t="n">
+        <v>40.05029238298302</v>
+      </c>
+      <c r="U173" t="n">
+        <v>59.26714927784489</v>
+      </c>
+      <c r="V173" t="n">
+        <v>71.37661355029205</v>
+      </c>
+      <c r="W173" t="n">
+        <v>48.27825526303367</v>
+      </c>
+      <c r="X173" t="n">
+        <v>47.15662088589901</v>
+      </c>
+      <c r="Y173" t="n">
+        <v>62.91254537696049</v>
+      </c>
+      <c r="Z173" t="n">
+        <v>77.85439352103452</v>
+      </c>
+      <c r="AA173" t="n">
+        <v>81.64233487766876</v>
+      </c>
+      <c r="AB173" t="n">
+        <v>77.40124191069415</v>
+      </c>
+      <c r="AC173" t="n">
+        <v>81.28137073602204</v>
+      </c>
+      <c r="AD173" t="n">
+        <v>77.28864272159554</v>
+      </c>
+      <c r="AE173" t="n">
+        <v>88.73867301656709</v>
+      </c>
+      <c r="AF173" t="n">
+        <v>81.22571803617082</v>
+      </c>
+      <c r="AG173" t="n">
+        <v>102.4787757564945</v>
+      </c>
+      <c r="AH173" t="n">
+        <v>129.3342590757308</v>
+      </c>
+      <c r="AI173" t="n">
+        <v>140.5097121999784</v>
+      </c>
+      <c r="AJ173" t="n">
+        <v>157.735812763147</v>
+      </c>
+      <c r="AK173" t="n">
+        <v>155.7385777786588</v>
+      </c>
+      <c r="AL173" t="n">
+        <v>128.714386587536</v>
+      </c>
+      <c r="AM173" t="n">
+        <v>171.1218339914561</v>
+      </c>
+      <c r="AN173" t="n">
+        <v>155.3389570121789</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>-0.1735227814236919</v>
+      </c>
+      <c r="AP173" t="n">
+        <v>0.32946936646495</v>
+      </c>
+      <c r="AQ173" t="n">
+        <v>-0.09223181292029181</v>
+      </c>
+      <c r="AR173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX173" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pimenta-do-reino</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>1.36920405739882</v>
+      </c>
+      <c r="D174" t="n">
+        <v>0.8806488110108636</v>
+      </c>
+      <c r="E174" t="n">
+        <v>0.7048451886412275</v>
+      </c>
+      <c r="F174" t="n">
+        <v>0.2746747436294347</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0.4039631651419262</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0.5308907333523941</v>
+      </c>
+      <c r="I174" t="n">
+        <v>0.541841758598625</v>
+      </c>
+      <c r="J174" t="n">
+        <v>0.4532233157943346</v>
+      </c>
+      <c r="K174" t="n">
+        <v>0.6148560552927452</v>
+      </c>
+      <c r="L174" t="n">
+        <v>0.811679503490962</v>
+      </c>
+      <c r="M174" t="n">
+        <v>1.190719717670189</v>
+      </c>
+      <c r="N174" t="n">
+        <v>1.664327867053835</v>
+      </c>
+      <c r="O174" t="n">
+        <v>0.8739101735731746</v>
+      </c>
+      <c r="P174" t="n">
+        <v>0.9952390448394119</v>
+      </c>
+      <c r="Q174" t="n">
+        <v>1.042689462137966</v>
+      </c>
+      <c r="R174" t="n">
+        <v>0.7622566966844967</v>
+      </c>
+      <c r="S174" t="n">
+        <v>0.7988169632309251</v>
+      </c>
+      <c r="T174" t="n">
+        <v>0.7559122974098131</v>
+      </c>
+      <c r="U174" t="n">
+        <v>0.9019019493545812</v>
+      </c>
+      <c r="V174" t="n">
+        <v>0.8701063851033679</v>
+      </c>
+      <c r="W174" t="n">
+        <v>0.7523339076633103</v>
+      </c>
+      <c r="X174" t="n">
+        <v>0.7867229082829587</v>
+      </c>
+      <c r="Y174" t="n">
+        <v>0.9691459629294444</v>
+      </c>
+      <c r="Z174" t="n">
+        <v>1.087678482946721</v>
+      </c>
+      <c r="AA174" t="n">
+        <v>1.096165896954756</v>
+      </c>
+      <c r="AB174" t="n">
+        <v>1.502398020604767</v>
+      </c>
+      <c r="AC174" t="n">
+        <v>2.610560576846941</v>
+      </c>
+      <c r="AD174" t="n">
+        <v>2.508490956061889</v>
+      </c>
+      <c r="AE174" t="n">
+        <v>2.510274949177162</v>
+      </c>
+      <c r="AF174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX174" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Soja</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>63.29204357665392</v>
+      </c>
+      <c r="D175" t="n">
+        <v>40.41707765821053</v>
+      </c>
+      <c r="E175" t="n">
+        <v>37.10379253143916</v>
+      </c>
+      <c r="F175" t="n">
+        <v>50.66034540294498</v>
+      </c>
+      <c r="G175" t="n">
+        <v>58.44647533869585</v>
+      </c>
+      <c r="H175" t="n">
+        <v>51.933189337976</v>
+      </c>
+      <c r="I175" t="n">
+        <v>42.4878945670499</v>
+      </c>
+      <c r="J175" t="n">
+        <v>49.43578700047006</v>
+      </c>
+      <c r="K175" t="n">
+        <v>60.45021761867743</v>
+      </c>
+      <c r="L175" t="n">
+        <v>57.87732444949693</v>
+      </c>
+      <c r="M175" t="n">
+        <v>60.22823059363535</v>
+      </c>
+      <c r="N175" t="n">
+        <v>60.86056442410639</v>
+      </c>
+      <c r="O175" t="n">
+        <v>78.92013771926881</v>
+      </c>
+      <c r="P175" t="n">
+        <v>109.4008783218881</v>
+      </c>
+      <c r="Q175" t="n">
+        <v>135.0318169012974</v>
+      </c>
+      <c r="R175" t="n">
+        <v>126.23098220976</v>
+      </c>
+      <c r="S175" t="n">
+        <v>90.15279477140669</v>
+      </c>
+      <c r="T175" t="n">
+        <v>78.8051223309556</v>
+      </c>
+      <c r="U175" t="n">
+        <v>99.9320072216774</v>
+      </c>
+      <c r="V175" t="n">
+        <v>130.4394258072307</v>
+      </c>
+      <c r="W175" t="n">
+        <v>126.5507163368919</v>
+      </c>
+      <c r="X175" t="n">
+        <v>123.9781080432808</v>
+      </c>
+      <c r="Y175" t="n">
+        <v>138.3768104613668</v>
+      </c>
+      <c r="Z175" t="n">
+        <v>161.6517165656232</v>
+      </c>
+      <c r="AA175" t="n">
+        <v>191.3471244573263</v>
+      </c>
+      <c r="AB175" t="n">
+        <v>193.7628504813011</v>
+      </c>
+      <c r="AC175" t="n">
+        <v>213.0409778519037</v>
+      </c>
+      <c r="AD175" t="n">
+        <v>214.4089031512444</v>
+      </c>
+      <c r="AE175" t="n">
+        <v>218.9430537934054</v>
+      </c>
+      <c r="AF175" t="n">
+        <v>245.4068645527506</v>
+      </c>
+      <c r="AG175" t="n">
+        <v>221.8346278497388</v>
+      </c>
+      <c r="AH175" t="n">
+        <v>316.888266328746</v>
+      </c>
+      <c r="AI175" t="n">
+        <v>404.2705745454077</v>
+      </c>
+      <c r="AJ175" t="n">
+        <v>355.6070620444721</v>
+      </c>
+      <c r="AK175" t="n">
+        <v>364.0734762433404</v>
+      </c>
+      <c r="AL175" t="n">
+        <v>306.1992930100286</v>
+      </c>
+      <c r="AM175" t="n">
+        <v>338.9825079051803</v>
+      </c>
+      <c r="AN175" t="n">
+        <v>335.8495665522325</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>-0.158962920975407</v>
+      </c>
+      <c r="AP175" t="n">
+        <v>0.1070649594676825</v>
+      </c>
+      <c r="AQ175" t="n">
+        <v>-0.009242191794227028</v>
+      </c>
+      <c r="AR175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX175" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Tomate</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>8.702802362587551</v>
+      </c>
+      <c r="D176" t="n">
+        <v>10.73444079845677</v>
+      </c>
+      <c r="E176" t="n">
+        <v>8.676655699461302</v>
+      </c>
+      <c r="F176" t="n">
+        <v>6.740956764866668</v>
+      </c>
+      <c r="G176" t="n">
+        <v>7.350314685660453</v>
+      </c>
+      <c r="H176" t="n">
+        <v>12.21484863575975</v>
+      </c>
+      <c r="I176" t="n">
+        <v>10.65010997240686</v>
+      </c>
+      <c r="J176" t="n">
+        <v>8.416865026513072</v>
+      </c>
+      <c r="K176" t="n">
+        <v>7.404604432740219</v>
+      </c>
+      <c r="L176" t="n">
+        <v>9.340707047259025</v>
+      </c>
+      <c r="M176" t="n">
+        <v>9.412093606518367</v>
+      </c>
+      <c r="N176" t="n">
+        <v>8.544629379531134</v>
+      </c>
+      <c r="O176" t="n">
+        <v>7.859585501579965</v>
+      </c>
+      <c r="P176" t="n">
+        <v>9.52228333069294</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>11.31369184077751</v>
+      </c>
+      <c r="R176" t="n">
+        <v>12.40073285597772</v>
+      </c>
+      <c r="S176" t="n">
+        <v>11.74549221005388</v>
+      </c>
+      <c r="T176" t="n">
+        <v>10.18200331107318</v>
+      </c>
+      <c r="U176" t="n">
+        <v>11.37613430876027</v>
+      </c>
+      <c r="V176" t="n">
+        <v>12.61303191868115</v>
+      </c>
+      <c r="W176" t="n">
+        <v>14.96507203577548</v>
+      </c>
+      <c r="X176" t="n">
+        <v>14.88848181760934</v>
+      </c>
+      <c r="Y176" t="n">
+        <v>16.34751774353948</v>
+      </c>
+      <c r="Z176" t="n">
+        <v>15.32022579351994</v>
+      </c>
+      <c r="AA176" t="n">
+        <v>29.1701623637988</v>
+      </c>
+      <c r="AB176" t="n">
+        <v>30.63896284804225</v>
+      </c>
+      <c r="AC176" t="n">
+        <v>28.40806398545322</v>
+      </c>
+      <c r="AD176" t="n">
+        <v>16.19542144733633</v>
+      </c>
+      <c r="AE176" t="n">
+        <v>15.29971186161397</v>
+      </c>
+      <c r="AF176" t="n">
+        <v>16.16520247211047</v>
+      </c>
+      <c r="AG176" t="n">
+        <v>16.68440639050867</v>
+      </c>
+      <c r="AH176" t="n">
+        <v>14.49214048240462</v>
+      </c>
+      <c r="AI176" t="n">
+        <v>12.78110571629041</v>
+      </c>
+      <c r="AJ176" t="n">
+        <v>15.74447345775637</v>
+      </c>
+      <c r="AK176" t="n">
+        <v>19.39647510034797</v>
+      </c>
+      <c r="AL176" t="n">
+        <v>21.05053829737856</v>
+      </c>
+      <c r="AM176" t="n">
+        <v>21.13308538375764</v>
+      </c>
+      <c r="AN176" t="n">
+        <v>23.11039356168499</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>0.08527648392160248</v>
+      </c>
+      <c r="AP176" t="n">
+        <v>0.003921376508901897</v>
+      </c>
+      <c r="AQ176" t="n">
+        <v>0.0935645762093531</v>
+      </c>
+      <c r="AR176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX176" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Trigo</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>11.46672039072572</v>
+      </c>
+      <c r="D177" t="n">
+        <v>5.085295294317471</v>
+      </c>
+      <c r="E177" t="n">
+        <v>4.588807450728084</v>
+      </c>
+      <c r="F177" t="n">
+        <v>5.509118548339181</v>
+      </c>
+      <c r="G177" t="n">
+        <v>3.616377954670428</v>
+      </c>
+      <c r="H177" t="n">
+        <v>3.07329349303798</v>
+      </c>
+      <c r="I177" t="n">
+        <v>2.223625394995323</v>
+      </c>
+      <c r="J177" t="n">
+        <v>5.737429955445666</v>
+      </c>
+      <c r="K177" t="n">
+        <v>3.186902995028573</v>
+      </c>
+      <c r="L177" t="n">
+        <v>2.859641115436669</v>
+      </c>
+      <c r="M177" t="n">
+        <v>3.57356320525283</v>
+      </c>
+      <c r="N177" t="n">
+        <v>2.425795289454816</v>
+      </c>
+      <c r="O177" t="n">
+        <v>4.964030114492371</v>
+      </c>
+      <c r="P177" t="n">
+        <v>5.991351439107909</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>11.80835061100909</v>
+      </c>
+      <c r="R177" t="n">
+        <v>9.197114613916407</v>
+      </c>
+      <c r="S177" t="n">
+        <v>5.861468198989829</v>
+      </c>
+      <c r="T177" t="n">
+        <v>3.021462474022518</v>
+      </c>
+      <c r="U177" t="n">
+        <v>6.184096959752381</v>
+      </c>
+      <c r="V177" t="n">
+        <v>9.389729127279473</v>
+      </c>
+      <c r="W177" t="n">
+        <v>6.496416740030659</v>
+      </c>
+      <c r="X177" t="n">
+        <v>7.27692957290734</v>
+      </c>
+      <c r="Y177" t="n">
+        <v>6.26971446673526</v>
+      </c>
+      <c r="Z177" t="n">
+        <v>7.515023412589997</v>
+      </c>
+      <c r="AA177" t="n">
+        <v>10.02498053890543</v>
+      </c>
+      <c r="AB177" t="n">
+        <v>8.569737540419082</v>
+      </c>
+      <c r="AC177" t="n">
+        <v>7.059191944526193</v>
+      </c>
+      <c r="AD177" t="n">
+        <v>9.241264660026671</v>
+      </c>
+      <c r="AE177" t="n">
+        <v>4.696349535558967</v>
+      </c>
+      <c r="AF177" t="n">
+        <v>7.56560218909372</v>
+      </c>
+      <c r="AG177" t="n">
+        <v>7.233228141039751</v>
+      </c>
+      <c r="AH177" t="n">
+        <v>10.50620718955907</v>
+      </c>
+      <c r="AI177" t="n">
+        <v>13.79918224012705</v>
+      </c>
+      <c r="AJ177" t="n">
+        <v>19.4203362657794</v>
+      </c>
+      <c r="AK177" t="n">
+        <v>11.32447448945247</v>
+      </c>
+      <c r="AL177" t="n">
+        <v>10.79959673448522</v>
+      </c>
+      <c r="AM177" t="n">
+        <v>10.71548680325851</v>
+      </c>
+      <c r="AN177" t="n">
+        <v>8.233837885307656</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>-0.04634897234799917</v>
+      </c>
+      <c r="AP177" t="n">
+        <v>-0.007788247403546888</v>
+      </c>
+      <c r="AQ177" t="n">
+        <v>-0.2315946035411289</v>
+      </c>
+      <c r="AR177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX177" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Uva</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>2.441624681524466</v>
+      </c>
+      <c r="D178" t="n">
+        <v>2.807334966077401</v>
+      </c>
+      <c r="E178" t="n">
+        <v>1.223819902745778</v>
+      </c>
+      <c r="F178" t="n">
+        <v>0.2710479376461857</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0.3835870113421433</v>
+      </c>
+      <c r="H178" t="n">
+        <v>1.409241454029316</v>
+      </c>
+      <c r="I178" t="n">
+        <v>2.411181347703066</v>
+      </c>
+      <c r="J178" t="n">
+        <v>1.035675923786852</v>
+      </c>
+      <c r="K178" t="n">
+        <v>1.735981707700465</v>
+      </c>
+      <c r="L178" t="n">
+        <v>5.567046498191591</v>
+      </c>
+      <c r="M178" t="n">
+        <v>4.606443263753214</v>
+      </c>
+      <c r="N178" t="n">
+        <v>1.816646912061801</v>
+      </c>
+      <c r="O178" t="n">
+        <v>3.758529650934039</v>
+      </c>
+      <c r="P178" t="n">
+        <v>3.549470950262391</v>
+      </c>
+      <c r="Q178" t="n">
+        <v>4.629410595050201</v>
+      </c>
+      <c r="R178" t="n">
+        <v>8.537873808973188</v>
+      </c>
+      <c r="S178" t="n">
+        <v>3.475182441614031</v>
+      </c>
+      <c r="T178" t="n">
+        <v>3.03833360633461</v>
+      </c>
+      <c r="U178" t="n">
+        <v>6.752942699562583</v>
+      </c>
+      <c r="V178" t="n">
+        <v>3.334378007943636</v>
+      </c>
+      <c r="W178" t="n">
+        <v>10.64297039659669</v>
+      </c>
+      <c r="X178" t="n">
+        <v>8.535060181424152</v>
+      </c>
+      <c r="Y178" t="n">
+        <v>11.59748035592994</v>
+      </c>
+      <c r="Z178" t="n">
+        <v>9.733954039664145</v>
+      </c>
+      <c r="AA178" t="n">
+        <v>8.508574247105981</v>
+      </c>
+      <c r="AB178" t="n">
+        <v>8.819636694648379</v>
+      </c>
+      <c r="AC178" t="n">
+        <v>7.357588806068785</v>
+      </c>
+      <c r="AD178" t="n">
+        <v>6.410747246911317</v>
+      </c>
+      <c r="AE178" t="n">
+        <v>10.57134573881076</v>
+      </c>
+      <c r="AF178" t="n">
+        <v>8.999466275871875</v>
+      </c>
+      <c r="AG178" t="n">
+        <v>8.78028695157283</v>
+      </c>
+      <c r="AH178" t="n">
+        <v>7.6580278026741</v>
+      </c>
+      <c r="AI178" t="n">
+        <v>7.50205219022136</v>
+      </c>
+      <c r="AJ178" t="n">
+        <v>6.849964920356497</v>
+      </c>
+      <c r="AK178" t="n">
+        <v>8.299575122998744</v>
+      </c>
+      <c r="AL178" t="n">
+        <v>11.48800362204004</v>
+      </c>
+      <c r="AM178" t="n">
+        <v>13.08796726726783</v>
+      </c>
+      <c r="AN178" t="n">
+        <v>12.19134393847717</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>0.3841676774761544</v>
+      </c>
+      <c r="AP178" t="n">
+        <v>0.1392725575188898</v>
+      </c>
+      <c r="AQ178" t="n">
+        <v>-0.06850745501427524</v>
+      </c>
+      <c r="AR178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX178" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Maçã</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y179" t="n">
+        <v>6.391489206537964</v>
+      </c>
+      <c r="Z179" t="n">
+        <v>6.828187414392831</v>
+      </c>
+      <c r="AA179" t="n">
+        <v>7.427797419269254</v>
+      </c>
+      <c r="AB179" t="n">
+        <v>8.289035770141874</v>
+      </c>
+      <c r="AC179" t="n">
+        <v>7.205712953743856</v>
+      </c>
+      <c r="AD179" t="n">
+        <v>8.041929483154727</v>
+      </c>
+      <c r="AE179" t="n">
+        <v>6.312330320157725</v>
+      </c>
+      <c r="AF179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AI179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AM179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AN179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AO179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AP179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AQ179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AR179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX179" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>TOTAL LAVOURAS</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>302.1107473346402</v>
+      </c>
+      <c r="D180" t="n">
+        <v>266.6639488556904</v>
+      </c>
+      <c r="E180" t="n">
+        <v>265.1991508706779</v>
+      </c>
+      <c r="F180" t="n">
+        <v>286.2037770981196</v>
+      </c>
+      <c r="G180" t="n">
+        <v>276.3990347345128</v>
+      </c>
+      <c r="H180" t="n">
+        <v>291.1347074461402</v>
+      </c>
+      <c r="I180" t="n">
+        <v>271.2440965696017</v>
+      </c>
+      <c r="J180" t="n">
+        <v>249.6086840149982</v>
+      </c>
+      <c r="K180" t="n">
+        <v>301.8277531912636</v>
+      </c>
+      <c r="L180" t="n">
+        <v>314.217319647099</v>
+      </c>
+      <c r="M180" t="n">
+        <v>314.1028433314031</v>
+      </c>
+      <c r="N180" t="n">
+        <v>290.028264960154</v>
+      </c>
+      <c r="O180" t="n">
+        <v>322.1677650359472</v>
+      </c>
+      <c r="P180" t="n">
+        <v>384.8405170663624</v>
+      </c>
+      <c r="Q180" t="n">
+        <v>436.7910473742746</v>
+      </c>
+      <c r="R180" t="n">
+        <v>433.5930197102998</v>
+      </c>
+      <c r="S180" t="n">
+        <v>366.5833367122299</v>
+      </c>
+      <c r="T180" t="n">
+        <v>368.8228169969373</v>
+      </c>
+      <c r="U180" t="n">
+        <v>416.5181524739404</v>
+      </c>
+      <c r="V180" t="n">
+        <v>478.265684973891</v>
+      </c>
+      <c r="W180" t="n">
+        <v>454.289056376364</v>
+      </c>
+      <c r="X180" t="n">
+        <v>471.1479587440304</v>
+      </c>
+      <c r="Y180" t="n">
+        <v>547.1801119451208</v>
+      </c>
+      <c r="Z180" t="n">
+        <v>576.9352079595582</v>
+      </c>
+      <c r="AA180" t="n">
+        <v>627.7091899167466</v>
+      </c>
+      <c r="AB180" t="n">
+        <v>635.7851825577693</v>
+      </c>
+      <c r="AC180" t="n">
+        <v>638.0920481377798</v>
+      </c>
+      <c r="AD180" t="n">
+        <v>646.1608756252475</v>
+      </c>
+      <c r="AE180" t="n">
+        <v>648.8436499572247</v>
+      </c>
+      <c r="AF180" t="n">
+        <v>626.7465583117468</v>
+      </c>
+      <c r="AG180" t="n">
+        <v>617.7335287842217</v>
+      </c>
+      <c r="AH180" t="n">
+        <v>753.0316581061886</v>
+      </c>
+      <c r="AI180" t="n">
+        <v>853.4637218717528</v>
+      </c>
+      <c r="AJ180" t="n">
+        <v>858.2888431898549</v>
+      </c>
+      <c r="AK180" t="n">
+        <v>893.185450510981</v>
+      </c>
+      <c r="AL180" t="n">
+        <v>866.4067969572791</v>
+      </c>
+      <c r="AM180" t="n">
+        <v>958.4802006644235</v>
+      </c>
+      <c r="AN180" t="n">
+        <v>893.1801677728128</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>-0.0299810678044321</v>
+      </c>
+      <c r="AP180" t="n">
+        <v>0.1062704078851824</v>
+      </c>
+      <c r="AQ180" t="n">
+        <v>-0.06812872383419544</v>
+      </c>
+      <c r="AR180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX180" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Bovinos</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" t="n">
+        <v>61.81286255328029</v>
+      </c>
+      <c r="O181" t="n">
+        <v>68.32835605892662</v>
+      </c>
+      <c r="P181" t="n">
+        <v>72.50929501842965</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>73.18076518798004</v>
+      </c>
+      <c r="R181" t="n">
+        <v>82.3370004449209</v>
+      </c>
+      <c r="S181" t="n">
+        <v>79.9374564613027</v>
+      </c>
+      <c r="T181" t="n">
+        <v>82.99476041205369</v>
+      </c>
+      <c r="U181" t="n">
+        <v>90.19612618577118</v>
+      </c>
+      <c r="V181" t="n">
+        <v>99.5871323995736</v>
+      </c>
+      <c r="W181" t="n">
+        <v>98.54842051597814</v>
+      </c>
+      <c r="X181" t="n">
+        <v>103.8996990379293</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>109.8381750096051</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>111.4753338404425</v>
+      </c>
+      <c r="AA181" t="n">
+        <v>120.7998329396349</v>
+      </c>
+      <c r="AB181" t="n">
+        <v>138.7770025104827</v>
+      </c>
+      <c r="AC181" t="n">
+        <v>143.5531729932068</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>134.3725359244551</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>131.8634328181109</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>132.7470752320562</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>142.1429393865724</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>163.046757434966</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>166.2647135230823</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>162.2394070529343</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>154.8907588098487</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>175.2678094248524</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>226.7073905101472</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>249.5667560353111</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>0.1315575620623017</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>0.2934913219609219</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>0.1008320261360898</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Suínos</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" t="n">
+        <v>11.19216385730796</v>
+      </c>
+      <c r="O182" t="n">
+        <v>13.42749175444433</v>
+      </c>
+      <c r="P182" t="n">
+        <v>13.76209938785545</v>
+      </c>
+      <c r="Q182" t="n">
+        <v>14.70807642381853</v>
+      </c>
+      <c r="R182" t="n">
+        <v>16.53649432689017</v>
+      </c>
+      <c r="S182" t="n">
+        <v>19.17260597717461</v>
+      </c>
+      <c r="T182" t="n">
+        <v>16.86506590936642</v>
+      </c>
+      <c r="U182" t="n">
+        <v>18.03396686304491</v>
+      </c>
+      <c r="V182" t="n">
+        <v>21.35405930507768</v>
+      </c>
+      <c r="W182" t="n">
+        <v>21.58569341688693</v>
+      </c>
+      <c r="X182" t="n">
+        <v>23.74642698511516</v>
+      </c>
+      <c r="Y182" t="n">
+        <v>23.78364267963148</v>
+      </c>
+      <c r="Z182" t="n">
+        <v>22.33163779243449</v>
+      </c>
+      <c r="AA182" t="n">
+        <v>25.85665753710301</v>
+      </c>
+      <c r="AB182" t="n">
+        <v>27.15780657551698</v>
+      </c>
+      <c r="AC182" t="n">
+        <v>29.02327637980187</v>
+      </c>
+      <c r="AD182" t="n">
+        <v>26.78426293859006</v>
+      </c>
+      <c r="AE182" t="n">
+        <v>39.92773855345582</v>
+      </c>
+      <c r="AF182" t="n">
+        <v>31.76881255257955</v>
+      </c>
+      <c r="AG182" t="n">
+        <v>39.32802514124855</v>
+      </c>
+      <c r="AH182" t="n">
+        <v>52.87350219556297</v>
+      </c>
+      <c r="AI182" t="n">
+        <v>49.12043151102717</v>
+      </c>
+      <c r="AJ182" t="n">
+        <v>42.85925568383897</v>
+      </c>
+      <c r="AK182" t="n">
+        <v>49.0361645860024</v>
+      </c>
+      <c r="AL182" t="n">
+        <v>57.51143978358328</v>
+      </c>
+      <c r="AM182" t="n">
+        <v>65.92886961994114</v>
+      </c>
+      <c r="AN182" t="n">
+        <v>51.68849894353571</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>0.1728372369481808</v>
+      </c>
+      <c r="AP182" t="n">
+        <v>0.146360965192887</v>
+      </c>
+      <c r="AQ182" t="n">
+        <v>-0.2159959780669169</v>
+      </c>
+      <c r="AR182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX182" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Frango</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" t="n">
+        <v>30.87599341732967</v>
+      </c>
+      <c r="O183" t="n">
+        <v>32.22267626600224</v>
+      </c>
+      <c r="P183" t="n">
+        <v>36.59146033157476</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>41.65619918220422</v>
+      </c>
+      <c r="R183" t="n">
+        <v>44.26051395812622</v>
+      </c>
+      <c r="S183" t="n">
+        <v>52.38554533094248</v>
+      </c>
+      <c r="T183" t="n">
+        <v>47.92578951684192</v>
+      </c>
+      <c r="U183" t="n">
+        <v>64.52606731045395</v>
+      </c>
+      <c r="V183" t="n">
+        <v>72.70088773176025</v>
+      </c>
+      <c r="W183" t="n">
+        <v>69.49434697084392</v>
+      </c>
+      <c r="X183" t="n">
+        <v>68.24523128675652</v>
+      </c>
+      <c r="Y183" t="n">
+        <v>73.40658423475652</v>
+      </c>
+      <c r="Z183" t="n">
+        <v>73.92380494568003</v>
+      </c>
+      <c r="AA183" t="n">
+        <v>82.01302636290471</v>
+      </c>
+      <c r="AB183" t="n">
+        <v>79.49502633838831</v>
+      </c>
+      <c r="AC183" t="n">
+        <v>84.61896919900771</v>
+      </c>
+      <c r="AD183" t="n">
+        <v>86.36384248943524</v>
+      </c>
+      <c r="AE183" t="n">
+        <v>78.55293204188763</v>
+      </c>
+      <c r="AF183" t="n">
+        <v>78.09507228619738</v>
+      </c>
+      <c r="AG183" t="n">
+        <v>91.00913891716156</v>
+      </c>
+      <c r="AH183" t="n">
+        <v>89.76727980919149</v>
+      </c>
+      <c r="AI183" t="n">
+        <v>104.7662472406295</v>
+      </c>
+      <c r="AJ183" t="n">
+        <v>102.1125153953184</v>
+      </c>
+      <c r="AK183" t="n">
+        <v>98.66857451604768</v>
+      </c>
+      <c r="AL183" t="n">
+        <v>109.8119956367381</v>
+      </c>
+      <c r="AM183" t="n">
+        <v>118.1803464477143</v>
+      </c>
+      <c r="AN183" t="n">
+        <v>107.3717821807364</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>0.1129378951236193</v>
+      </c>
+      <c r="AP183" t="n">
+        <v>0.07620616274618097</v>
+      </c>
+      <c r="AQ183" t="n">
+        <v>-0.09145822120059366</v>
+      </c>
+      <c r="AR183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX183" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Leite</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N184" t="n">
+        <v>24.41542581884059</v>
+      </c>
+      <c r="O184" t="n">
+        <v>23.49450715898349</v>
+      </c>
+      <c r="P184" t="n">
+        <v>23.79008359239364</v>
+      </c>
+      <c r="Q184" t="n">
+        <v>26.19802422938563</v>
+      </c>
+      <c r="R184" t="n">
+        <v>26.77565300678248</v>
+      </c>
+      <c r="S184" t="n">
+        <v>30.11502707823685</v>
+      </c>
+      <c r="T184" t="n">
+        <v>28.7650201066187</v>
+      </c>
+      <c r="U184" t="n">
+        <v>35.36228463351219</v>
+      </c>
+      <c r="V184" t="n">
+        <v>39.78058098854056</v>
+      </c>
+      <c r="W184" t="n">
+        <v>40.55673991820887</v>
+      </c>
+      <c r="X184" t="n">
+        <v>44.78922382700527</v>
+      </c>
+      <c r="Y184" t="n">
+        <v>46.17238713269023</v>
+      </c>
+      <c r="Z184" t="n">
+        <v>48.24836054371472</v>
+      </c>
+      <c r="AA184" t="n">
+        <v>55.83288974648612</v>
+      </c>
+      <c r="AB184" t="n">
+        <v>60.29206443646039</v>
+      </c>
+      <c r="AC184" t="n">
+        <v>54.42389453613039</v>
+      </c>
+      <c r="AD184" t="n">
+        <v>50.49913601869668</v>
+      </c>
+      <c r="AE184" t="n">
+        <v>56.26643325694708</v>
+      </c>
+      <c r="AF184" t="n">
+        <v>55.43008241289246</v>
+      </c>
+      <c r="AG184" t="n">
+        <v>54.91639650691847</v>
+      </c>
+      <c r="AH184" t="n">
+        <v>56.46170267134205</v>
+      </c>
+      <c r="AI184" t="n">
+        <v>56.52397954038796</v>
+      </c>
+      <c r="AJ184" t="n">
+        <v>61.71283644379032</v>
+      </c>
+      <c r="AK184" t="n">
+        <v>69.39626156646942</v>
+      </c>
+      <c r="AL184" t="n">
+        <v>70.32095374049825</v>
+      </c>
+      <c r="AM184" t="n">
+        <v>76.9913115524645</v>
+      </c>
+      <c r="AN184" t="n">
+        <v>74.43605744160425</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>0.01332481250655193</v>
+      </c>
+      <c r="AP184" t="n">
+        <v>0.09485590648530606</v>
+      </c>
+      <c r="AQ184" t="n">
+        <v>-0.03318886325399206</v>
+      </c>
+      <c r="AR184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX184" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Ovos</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N185" t="n">
+        <v>9.546279771901451</v>
+      </c>
+      <c r="O185" t="n">
+        <v>9.407074374260525</v>
+      </c>
+      <c r="P185" t="n">
+        <v>9.691908508871332</v>
+      </c>
+      <c r="Q185" t="n">
+        <v>11.72351385038528</v>
+      </c>
+      <c r="R185" t="n">
+        <v>11.88191618229581</v>
+      </c>
+      <c r="S185" t="n">
+        <v>11.96269011674369</v>
+      </c>
+      <c r="T185" t="n">
+        <v>11.36334680796197</v>
+      </c>
+      <c r="U185" t="n">
+        <v>12.07683781382413</v>
+      </c>
+      <c r="V185" t="n">
+        <v>13.03668278145508</v>
+      </c>
+      <c r="W185" t="n">
+        <v>13.00462560352417</v>
+      </c>
+      <c r="X185" t="n">
+        <v>12.6484749142983</v>
+      </c>
+      <c r="Y185" t="n">
+        <v>14.90418536528397</v>
+      </c>
+      <c r="Z185" t="n">
+        <v>17.47135576735928</v>
+      </c>
+      <c r="AA185" t="n">
+        <v>20.54857021857906</v>
+      </c>
+      <c r="AB185" t="n">
+        <v>23.08712453466336</v>
+      </c>
+      <c r="AC185" t="n">
+        <v>23.50671495040903</v>
+      </c>
+      <c r="AD185" t="n">
+        <v>25.34248773387342</v>
+      </c>
+      <c r="AE185" t="n">
+        <v>20.88424631951071</v>
+      </c>
+      <c r="AF185" t="n">
+        <v>18.99745151225207</v>
+      </c>
+      <c r="AG185" t="n">
+        <v>19.23727592975403</v>
+      </c>
+      <c r="AH185" t="n">
+        <v>21.1263596501873</v>
+      </c>
+      <c r="AI185" t="n">
+        <v>19.79757585714383</v>
+      </c>
+      <c r="AJ185" t="n">
+        <v>21.96603737647138</v>
+      </c>
+      <c r="AK185" t="n">
+        <v>27.06686775066731</v>
+      </c>
+      <c r="AL185" t="n">
+        <v>27.53946121911159</v>
+      </c>
+      <c r="AM185" t="n">
+        <v>30.43228777068913</v>
+      </c>
+      <c r="AN185" t="n">
+        <v>28.0757708617977</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>0.01746022010369597</v>
+      </c>
+      <c r="AP185" t="n">
+        <v>0.1050429610282282</v>
+      </c>
+      <c r="AQ185" t="n">
+        <v>-0.07743476029958907</v>
+      </c>
+      <c r="AR185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX185" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>TOTAL PECUÁRIA</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N186" t="n">
+        <v>137.84272541866</v>
+      </c>
+      <c r="O186" t="n">
+        <v>146.8801056126172</v>
+      </c>
+      <c r="P186" t="n">
+        <v>156.3448468391248</v>
+      </c>
+      <c r="Q186" t="n">
+        <v>167.4665788737737</v>
+      </c>
+      <c r="R186" t="n">
+        <v>181.7915779190156</v>
+      </c>
+      <c r="S186" t="n">
+        <v>193.5733249644003</v>
+      </c>
+      <c r="T186" t="n">
+        <v>187.9139827528427</v>
+      </c>
+      <c r="U186" t="n">
+        <v>220.1952828066064</v>
+      </c>
+      <c r="V186" t="n">
+        <v>246.4593432064072</v>
+      </c>
+      <c r="W186" t="n">
+        <v>243.189826425442</v>
+      </c>
+      <c r="X186" t="n">
+        <v>253.3290560511045</v>
+      </c>
+      <c r="Y186" t="n">
+        <v>268.1049744219673</v>
+      </c>
+      <c r="Z186" t="n">
+        <v>273.4504928896311</v>
+      </c>
+      <c r="AA186" t="n">
+        <v>305.0509768047078</v>
+      </c>
+      <c r="AB186" t="n">
+        <v>328.8090243955118</v>
+      </c>
+      <c r="AC186" t="n">
+        <v>335.1260280585558</v>
+      </c>
+      <c r="AD186" t="n">
+        <v>323.3622651050505</v>
+      </c>
+      <c r="AE186" t="n">
+        <v>327.4947829899121</v>
+      </c>
+      <c r="AF186" t="n">
+        <v>317.0384939959777</v>
+      </c>
+      <c r="AG186" t="n">
+        <v>346.633775881655</v>
+      </c>
+      <c r="AH186" t="n">
+        <v>383.2756017612498</v>
+      </c>
+      <c r="AI186" t="n">
+        <v>396.4729476722708</v>
+      </c>
+      <c r="AJ186" t="n">
+        <v>390.8900519523534</v>
+      </c>
+      <c r="AK186" t="n">
+        <v>399.0586272290356</v>
+      </c>
+      <c r="AL186" t="n">
+        <v>440.4516598047835</v>
+      </c>
+      <c r="AM186" t="n">
+        <v>518.2402059009562</v>
+      </c>
+      <c r="AN186" t="n">
+        <v>511.1388654629852</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>0.1037266951554736</v>
+      </c>
+      <c r="AP186" t="n">
+        <v>0.1766108592499118</v>
+      </c>
+      <c r="AQ186" t="n">
+        <v>-0.01370279719155598</v>
+      </c>
+      <c r="AR186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX186" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>VBP TOTAL</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>302.1107473346402</v>
+      </c>
+      <c r="D187" t="n">
+        <v>266.6639488556904</v>
+      </c>
+      <c r="E187" t="n">
+        <v>265.1991508706779</v>
+      </c>
+      <c r="F187" t="n">
+        <v>286.2037770981196</v>
+      </c>
+      <c r="G187" t="n">
+        <v>276.3990347345128</v>
+      </c>
+      <c r="H187" t="n">
+        <v>291.1347074461402</v>
+      </c>
+      <c r="I187" t="n">
+        <v>271.2440965696017</v>
+      </c>
+      <c r="J187" t="n">
+        <v>249.6086840149982</v>
+      </c>
+      <c r="K187" t="n">
+        <v>301.8277531912636</v>
+      </c>
+      <c r="L187" t="n">
+        <v>314.217319647099</v>
+      </c>
+      <c r="M187" t="n">
+        <v>314.1028433314031</v>
+      </c>
+      <c r="N187" t="n">
+        <v>427.870990378814</v>
+      </c>
+      <c r="O187" t="n">
+        <v>469.0478706485644</v>
+      </c>
+      <c r="P187" t="n">
+        <v>541.1853639054873</v>
+      </c>
+      <c r="Q187" t="n">
+        <v>604.2576262480484</v>
+      </c>
+      <c r="R187" t="n">
+        <v>615.3845976293153</v>
+      </c>
+      <c r="S187" t="n">
+        <v>560.1566616766303</v>
+      </c>
+      <c r="T187" t="n">
+        <v>556.7367997497799</v>
+      </c>
+      <c r="U187" t="n">
+        <v>636.7134352805467</v>
+      </c>
+      <c r="V187" t="n">
+        <v>724.7250281802982</v>
+      </c>
+      <c r="W187" t="n">
+        <v>697.478882801806</v>
+      </c>
+      <c r="X187" t="n">
+        <v>724.4770147951349</v>
+      </c>
+      <c r="Y187" t="n">
+        <v>815.2850863670881</v>
+      </c>
+      <c r="Z187" t="n">
+        <v>850.3857008491892</v>
+      </c>
+      <c r="AA187" t="n">
+        <v>932.7601667214544</v>
+      </c>
+      <c r="AB187" t="n">
+        <v>964.5942069532811</v>
+      </c>
+      <c r="AC187" t="n">
+        <v>973.2180761963356</v>
+      </c>
+      <c r="AD187" t="n">
+        <v>969.5231407302981</v>
+      </c>
+      <c r="AE187" t="n">
+        <v>976.3384329471368</v>
+      </c>
+      <c r="AF187" t="n">
+        <v>943.7850523077245</v>
+      </c>
+      <c r="AG187" t="n">
+        <v>964.3673046658766</v>
+      </c>
+      <c r="AH187" t="n">
+        <v>1136.307259867438</v>
+      </c>
+      <c r="AI187" t="n">
+        <v>1249.936669544024</v>
+      </c>
+      <c r="AJ187" t="n">
+        <v>1249.178895142208</v>
+      </c>
+      <c r="AK187" t="n">
+        <v>1292.244077740017</v>
+      </c>
+      <c r="AL187" t="n">
+        <v>1306.858456762063</v>
+      </c>
+      <c r="AM187" t="n">
+        <v>1476.72040656538</v>
+      </c>
+      <c r="AN187" t="n">
+        <v>1404.319033235798</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>0.01130930237854511</v>
+      </c>
+      <c r="AP187" t="n">
+        <v>0.1299773123282038</v>
+      </c>
+      <c r="AQ187" t="n">
+        <v>-0.04902849111293583</v>
+      </c>
+      <c r="AR187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX187" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>2026 - 06</t>
+        </is>
+      </c>
+      <c r="B188" t="n">
+        <v>0</v>
+      </c>
+      <c r="C188" t="n">
+        <v>0</v>
+      </c>
+      <c r="D188" t="n">
+        <v>0</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+      <c r="I188" t="n">
+        <v>0</v>
+      </c>
+      <c r="J188" t="n">
+        <v>0</v>
+      </c>
+      <c r="K188" t="n">
+        <v>0</v>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="n">
+        <v>0</v>
+      </c>
+      <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="O188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="R188" t="n">
+        <v>0</v>
+      </c>
+      <c r="S188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
+        <v>0</v>
+      </c>
+      <c r="U188" t="n">
+        <v>0</v>
+      </c>
+      <c r="V188" t="n">
+        <v>0</v>
+      </c>
+      <c r="W188" t="n">
+        <v>0</v>
+      </c>
+      <c r="X188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y188" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ188" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR188" t="inlineStr">
         <is>
           <t>RO</t>
         </is>
       </c>
-      <c r="AS157" t="inlineStr">
+      <c r="AS188" t="inlineStr">
         <is>
           <t>ALGODÃO</t>
         </is>
       </c>
-      <c r="AT157" t="n">
+      <c r="AT188" t="n">
         <v>2018</v>
       </c>
-      <c r="AU157" t="n">
-        <v>92227272.73720001</v>
-      </c>
-      <c r="AV157" t="n">
-        <v>92.2273</v>
-      </c>
-      <c r="AW157" t="inlineStr">
+      <c r="AU188" t="n">
+        <v>91501832.99869999</v>
+      </c>
+      <c r="AV188" t="n">
+        <v>91.5018</v>
+      </c>
+      <c r="AW188" t="inlineStr">
         <is>
           <t>LAVOURAS</t>
         </is>
       </c>
-      <c r="AX157" t="inlineStr">
+      <c r="AX188" t="inlineStr">
         <is>
           <t>RONDÔNIA</t>
         </is>
       </c>
-      <c r="AY157" t="inlineStr">
+      <c r="AY188" t="inlineStr">
         <is>
           <t>NORTE</t>
         </is>
